--- a/scripts/pdf-to-knowledge/objects-pdf/all-objects-sections.xlsx
+++ b/scripts/pdf-to-knowledge/objects-pdf/all-objects-sections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004bjuu\Documents\knowledge_of_plant_simulation\scripts\pdf-to-knowledge\objects-pdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EE93AC-02AC-49C3-A729-156E75D404FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790B68AF-B7F3-464D-9175-780E34E86C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-2604" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
   <si>
     <t>Path</t>
   </si>
@@ -1038,6 +1038,111 @@
   </si>
   <si>
     <t>simtalk\deprecated-unsupported-names\2d-visualization</t>
+  </si>
+  <si>
+    <t>step-by-step\onboarding-plant-simulation\step-by-step-help</t>
+  </si>
+  <si>
+    <t>step-by-step\onboarding-plant-simulation\modeling</t>
+  </si>
+  <si>
+    <t>step-by-step\onboarding-plant-simulation\getting-started-ui-basic-operations</t>
+  </si>
+  <si>
+    <t>step-by-step\core-model-construction-workflow\material-flow</t>
+  </si>
+  <si>
+    <t>step-by-step\core-model-construction-workflow\classes-libraries-toolboxes</t>
+  </si>
+  <si>
+    <t>step-by-step\core-model-construction-workflow\frame-modeling-simulation-control-drag-drop</t>
+  </si>
+  <si>
+    <t>step-by-step\material-flow-fundamentals\sources-routing-transfer-logic</t>
+  </si>
+  <si>
+    <t>step-by-step\material-flow-fundamentals\processing-setup-failures-buffers-inventory</t>
+  </si>
+  <si>
+    <t>step-by-step\material-flow-fundamentals\pull-systems-carriers-line-balancing</t>
+  </si>
+  <si>
+    <t>step-by-step\advanced-material-flow-behavior\randomness-distributions</t>
+  </si>
+  <si>
+    <t>step-by-step\advanced-material-flow-behavior\controls-sensors-observers-distance-control</t>
+  </si>
+  <si>
+    <t>step-by-step\fluids-energy-workforce-shift-logic\free-flowing-materials</t>
+  </si>
+  <si>
+    <t>step-by-step\fluids-energy-workforce-shift-logic\cost-power-analysis</t>
+  </si>
+  <si>
+    <t>step-by-step\fluids-energy-workforce-shift-logic\worker-modeling-job-execution</t>
+  </si>
+  <si>
+    <t>step-by-step\fluids-energy-workforce-shift-logic\calendars-lockout-zones</t>
+  </si>
+  <si>
+    <t>step-by-step\assembly-robots-conveyance-patterns\dismantling-workflows</t>
+  </si>
+  <si>
+    <t>step-by-step\assembly-robots-conveyance-patterns\pick-place-robot-scenarios</t>
+  </si>
+  <si>
+    <t>step-by-step\assembly-robots-conveyance-patterns\converter-turntable-based-routing</t>
+  </si>
+  <si>
+    <t>step-by-step\transport-systems-experimentation\conveyor-track-agv-battery</t>
+  </si>
+  <si>
+    <t>step-by-step\transport-systems-experimentation\data-fit-preparation-distribution-fitting</t>
+  </si>
+  <si>
+    <t>step-by-step\transport-systems-experimentation\experiment-manager-genetic-optimization</t>
+  </si>
+  <si>
+    <t>step-by-step\transport-systems-experimentation\packaging-sharing-models</t>
+  </si>
+  <si>
+    <t>step-by-step\3-d-scene-object-foundations\navigation-camera-grid-control</t>
+  </si>
+  <si>
+    <t>step-by-step\3-d-scene-object-foundations\placement-transformation-frame-editing</t>
+  </si>
+  <si>
+    <t>step-by-step\graphics-animation-authoring\state-visualization</t>
+  </si>
+  <si>
+    <t>step-by-step\graphics-animation-authoring\building-capable-simulation-objects</t>
+  </si>
+  <si>
+    <t>step-by-step\graphics-animation-authoring\paths-mu-joints-poses</t>
+  </si>
+  <si>
+    <t>step-by-step\realism-media-omniverse-output\realistic-scene-construction-graphic-optimization</t>
+  </si>
+  <si>
+    <t>step-by-step\realism-media-omniverse-output\model-optimization-video-publishing</t>
+  </si>
+  <si>
+    <t>step-by-step\runtime-animation-statistics-interaction\icon-behavior</t>
+  </si>
+  <si>
+    <t>step-by-step\runtime-animation-statistics-interaction\charts-reports-visual-analytics</t>
+  </si>
+  <si>
+    <t>step-by-step\runtime-animation-statistics-interaction\interactive-controls-state-toggles-actions</t>
+  </si>
+  <si>
+    <t>step-by-step\data-integration-parameterization\import-export-databases-external-media</t>
+  </si>
+  <si>
+    <t>step-by-step\data-integration-parameterization\lists-tables-network-socket-exchange</t>
+  </si>
+  <si>
+    <t>step-by-step\data-integration-parameterization\dialog-based-attribute-explorer</t>
   </si>
 </sst>
 </file>
@@ -1090,10 +1195,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1381,13 +1482,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D332"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D367"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="99.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="99.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1416,7 +1517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1431,7 +1532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1446,7 +1547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1461,7 +1562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1476,7 +1577,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1491,7 +1592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1506,7 +1607,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1521,7 +1622,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1536,7 +1637,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1551,7 +1652,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1566,7 +1667,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1581,7 +1682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1596,7 +1697,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1611,7 +1712,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1626,7 +1727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1641,7 +1742,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1656,7 +1757,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1671,7 +1772,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1686,7 +1787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1701,7 +1802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1716,7 +1817,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1731,7 +1832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1746,7 +1847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1761,7 +1862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1776,7 +1877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1791,7 +1892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1806,7 +1907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1821,7 +1922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -1836,7 +1937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -1851,7 +1952,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -1866,7 +1967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -1881,7 +1982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -1896,7 +1997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1911,7 +2012,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -1926,7 +2027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1941,7 +2042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1956,7 +2057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -1971,7 +2072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -1986,7 +2087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -2001,7 +2102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -2016,7 +2117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -2031,7 +2132,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -2046,7 +2147,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -2061,7 +2162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -2076,7 +2177,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -2091,7 +2192,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -2106,7 +2207,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -2121,7 +2222,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -2136,7 +2237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -2151,7 +2252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -2166,7 +2267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -2181,7 +2282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -2196,7 +2297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -2211,7 +2312,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -2226,7 +2327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -2241,7 +2342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -2256,7 +2357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -2271,7 +2372,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -2286,7 +2387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -2301,7 +2402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -2316,7 +2417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -2331,7 +2432,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -2346,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -2361,7 +2462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -2376,7 +2477,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -2391,7 +2492,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -2406,7 +2507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -2421,7 +2522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -2436,7 +2537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -2451,7 +2552,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -2466,7 +2567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -2481,7 +2582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -2496,7 +2597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -2511,7 +2612,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -2526,7 +2627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -2541,7 +2642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -2556,7 +2657,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -2571,7 +2672,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -2586,7 +2687,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -2601,7 +2702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -2616,7 +2717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -2631,7 +2732,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -2646,7 +2747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -2661,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -2676,7 +2777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -2691,7 +2792,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -2706,7 +2807,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -2721,7 +2822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -2736,7 +2837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -2751,7 +2852,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -2766,7 +2867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -2781,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -2796,7 +2897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -2811,7 +2912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -2826,7 +2927,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -2841,7 +2942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -2856,7 +2957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>101</v>
       </c>
@@ -2871,7 +2972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>102</v>
       </c>
@@ -2886,7 +2987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>103</v>
       </c>
@@ -2901,7 +3002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>104</v>
       </c>
@@ -2916,7 +3017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -2931,7 +3032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>106</v>
       </c>
@@ -2946,7 +3047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>107</v>
       </c>
@@ -2961,7 +3062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>108</v>
       </c>
@@ -2976,7 +3077,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>109</v>
       </c>
@@ -2991,7 +3092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>110</v>
       </c>
@@ -3006,7 +3107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>111</v>
       </c>
@@ -3021,7 +3122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>112</v>
       </c>
@@ -3036,7 +3137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>113</v>
       </c>
@@ -3051,7 +3152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -3066,7 +3167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -3081,7 +3182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -3096,7 +3197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -3111,7 +3212,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -3126,7 +3227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>119</v>
       </c>
@@ -3141,7 +3242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -3156,7 +3257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -3171,7 +3272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>122</v>
       </c>
@@ -3186,7 +3287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>123</v>
       </c>
@@ -3201,7 +3302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>124</v>
       </c>
@@ -3216,7 +3317,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>125</v>
       </c>
@@ -3231,7 +3332,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>126</v>
       </c>
@@ -3246,7 +3347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>127</v>
       </c>
@@ -3261,7 +3362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>128</v>
       </c>
@@ -3276,7 +3377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>129</v>
       </c>
@@ -3291,7 +3392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>130</v>
       </c>
@@ -3306,7 +3407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>131</v>
       </c>
@@ -3321,7 +3422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>132</v>
       </c>
@@ -3336,7 +3437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>133</v>
       </c>
@@ -3351,7 +3452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>134</v>
       </c>
@@ -3366,7 +3467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>135</v>
       </c>
@@ -3381,7 +3482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>136</v>
       </c>
@@ -3396,7 +3497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>137</v>
       </c>
@@ -3411,7 +3512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>138</v>
       </c>
@@ -3426,7 +3527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -3441,7 +3542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -3456,7 +3557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>141</v>
       </c>
@@ -3471,7 +3572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -3486,7 +3587,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>143</v>
       </c>
@@ -3501,7 +3602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>144</v>
       </c>
@@ -3516,7 +3617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>145</v>
       </c>
@@ -3531,7 +3632,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>146</v>
       </c>
@@ -3546,7 +3647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>147</v>
       </c>
@@ -3561,7 +3662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>148</v>
       </c>
@@ -3576,7 +3677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>149</v>
       </c>
@@ -3591,7 +3692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -3606,7 +3707,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>151</v>
       </c>
@@ -3621,7 +3722,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>152</v>
       </c>
@@ -3636,7 +3737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>153</v>
       </c>
@@ -3651,7 +3752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>154</v>
       </c>
@@ -3666,7 +3767,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>155</v>
       </c>
@@ -3681,7 +3782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>156</v>
       </c>
@@ -3696,7 +3797,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>157</v>
       </c>
@@ -3711,7 +3812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>158</v>
       </c>
@@ -3726,7 +3827,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>159</v>
       </c>
@@ -3741,7 +3842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>160</v>
       </c>
@@ -3756,7 +3857,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>161</v>
       </c>
@@ -3771,7 +3872,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -3786,7 +3887,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>163</v>
       </c>
@@ -3801,7 +3902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>164</v>
       </c>
@@ -3816,7 +3917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>165</v>
       </c>
@@ -3831,7 +3932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>166</v>
       </c>
@@ -3846,7 +3947,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>167</v>
       </c>
@@ -3861,7 +3962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>168</v>
       </c>
@@ -3876,7 +3977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>169</v>
       </c>
@@ -3891,7 +3992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>170</v>
       </c>
@@ -3906,7 +4007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>171</v>
       </c>
@@ -3921,7 +4022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>172</v>
       </c>
@@ -3936,7 +4037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>173</v>
       </c>
@@ -3951,7 +4052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>174</v>
       </c>
@@ -3966,7 +4067,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>175</v>
       </c>
@@ -3981,7 +4082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>176</v>
       </c>
@@ -3996,7 +4097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>177</v>
       </c>
@@ -4011,7 +4112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>178</v>
       </c>
@@ -4026,7 +4127,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>179</v>
       </c>
@@ -4041,7 +4142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>180</v>
       </c>
@@ -4056,7 +4157,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>181</v>
       </c>
@@ -4071,7 +4172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>182</v>
       </c>
@@ -4086,7 +4187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>183</v>
       </c>
@@ -4101,7 +4202,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>184</v>
       </c>
@@ -4116,7 +4217,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>185</v>
       </c>
@@ -4131,7 +4232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>186</v>
       </c>
@@ -4146,7 +4247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>187</v>
       </c>
@@ -4161,7 +4262,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>188</v>
       </c>
@@ -4176,7 +4277,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>189</v>
       </c>
@@ -4191,7 +4292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>190</v>
       </c>
@@ -4206,7 +4307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>191</v>
       </c>
@@ -4221,7 +4322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>192</v>
       </c>
@@ -4236,7 +4337,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>193</v>
       </c>
@@ -4251,7 +4352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>194</v>
       </c>
@@ -4266,7 +4367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>195</v>
       </c>
@@ -4281,7 +4382,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>196</v>
       </c>
@@ -4296,7 +4397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>197</v>
       </c>
@@ -4311,7 +4412,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>198</v>
       </c>
@@ -4326,7 +4427,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -4341,7 +4442,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>200</v>
       </c>
@@ -4356,7 +4457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>201</v>
       </c>
@@ -4371,7 +4472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>202</v>
       </c>
@@ -4386,7 +4487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>203</v>
       </c>
@@ -4401,7 +4502,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>204</v>
       </c>
@@ -4416,7 +4517,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>205</v>
       </c>
@@ -4431,7 +4532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>206</v>
       </c>
@@ -4446,7 +4547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>207</v>
       </c>
@@ -4461,7 +4562,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>208</v>
       </c>
@@ -4476,7 +4577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>209</v>
       </c>
@@ -4491,7 +4592,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>210</v>
       </c>
@@ -4506,7 +4607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>211</v>
       </c>
@@ -4521,7 +4622,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>212</v>
       </c>
@@ -4536,7 +4637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>213</v>
       </c>
@@ -4551,7 +4652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>214</v>
       </c>
@@ -4566,7 +4667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>215</v>
       </c>
@@ -4581,7 +4682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>216</v>
       </c>
@@ -4596,7 +4697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>217</v>
       </c>
@@ -4611,7 +4712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>218</v>
       </c>
@@ -4626,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>219</v>
       </c>
@@ -4641,7 +4742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>220</v>
       </c>
@@ -4656,7 +4757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>221</v>
       </c>
@@ -4671,7 +4772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>222</v>
       </c>
@@ -4686,7 +4787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>223</v>
       </c>
@@ -4701,7 +4802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>224</v>
       </c>
@@ -4716,7 +4817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>225</v>
       </c>
@@ -4731,7 +4832,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>226</v>
       </c>
@@ -4746,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>227</v>
       </c>
@@ -4761,7 +4862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>228</v>
       </c>
@@ -4776,7 +4877,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>229</v>
       </c>
@@ -4791,7 +4892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>230</v>
       </c>
@@ -4806,7 +4907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>231</v>
       </c>
@@ -4821,7 +4922,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>232</v>
       </c>
@@ -4836,7 +4937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>233</v>
       </c>
@@ -4851,7 +4952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>234</v>
       </c>
@@ -4866,7 +4967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>235</v>
       </c>
@@ -4881,7 +4982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>236</v>
       </c>
@@ -4896,7 +4997,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>237</v>
       </c>
@@ -4911,7 +5012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>238</v>
       </c>
@@ -4926,7 +5027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>239</v>
       </c>
@@ -4941,7 +5042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>240</v>
       </c>
@@ -4956,7 +5057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>241</v>
       </c>
@@ -4971,7 +5072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>242</v>
       </c>
@@ -4986,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>243</v>
       </c>
@@ -5001,7 +5102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>244</v>
       </c>
@@ -5016,7 +5117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>245</v>
       </c>
@@ -5031,7 +5132,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>246</v>
       </c>
@@ -5046,7 +5147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>247</v>
       </c>
@@ -5061,7 +5162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>248</v>
       </c>
@@ -5076,7 +5177,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>249</v>
       </c>
@@ -5091,7 +5192,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>250</v>
       </c>
@@ -5106,7 +5207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>251</v>
       </c>
@@ -5121,7 +5222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>252</v>
       </c>
@@ -5136,7 +5237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>253</v>
       </c>
@@ -5151,7 +5252,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>254</v>
       </c>
@@ -5166,7 +5267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>255</v>
       </c>
@@ -5181,7 +5282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>256</v>
       </c>
@@ -5196,7 +5297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>257</v>
       </c>
@@ -5211,7 +5312,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>258</v>
       </c>
@@ -5226,7 +5327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>259</v>
       </c>
@@ -5241,7 +5342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>260</v>
       </c>
@@ -5252,11 +5353,11 @@
         <v>7570</v>
       </c>
       <c r="D258">
-        <f t="shared" ref="D258:D321" si="4">C258-B258</f>
+        <f t="shared" ref="D258:D294" si="4">C258-B258</f>
         <v>15</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>261</v>
       </c>
@@ -5271,7 +5372,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>262</v>
       </c>
@@ -5286,7 +5387,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>263</v>
       </c>
@@ -5301,7 +5402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>264</v>
       </c>
@@ -5316,7 +5417,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>265</v>
       </c>
@@ -5331,7 +5432,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>266</v>
       </c>
@@ -5346,7 +5447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>267</v>
       </c>
@@ -5361,7 +5462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>268</v>
       </c>
@@ -5376,7 +5477,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>269</v>
       </c>
@@ -5391,7 +5492,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>270</v>
       </c>
@@ -5406,7 +5507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>271</v>
       </c>
@@ -5421,7 +5522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>272</v>
       </c>
@@ -5436,7 +5537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>273</v>
       </c>
@@ -5451,7 +5552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>274</v>
       </c>
@@ -5466,7 +5567,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>275</v>
       </c>
@@ -5481,7 +5582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>276</v>
       </c>
@@ -5496,7 +5597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>277</v>
       </c>
@@ -5511,7 +5612,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>278</v>
       </c>
@@ -5526,7 +5627,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>279</v>
       </c>
@@ -5541,7 +5642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>280</v>
       </c>
@@ -5556,7 +5657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>281</v>
       </c>
@@ -5571,7 +5672,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>282</v>
       </c>
@@ -5586,7 +5687,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>283</v>
       </c>
@@ -5601,7 +5702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>284</v>
       </c>
@@ -5616,7 +5717,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>285</v>
       </c>
@@ -5631,7 +5732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>286</v>
       </c>
@@ -5646,7 +5747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>287</v>
       </c>
@@ -5661,7 +5762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>288</v>
       </c>
@@ -5676,7 +5777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>289</v>
       </c>
@@ -5691,7 +5792,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>290</v>
       </c>
@@ -5706,7 +5807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>291</v>
       </c>
@@ -5721,7 +5822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>292</v>
       </c>
@@ -5736,7 +5837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>293</v>
       </c>
@@ -5751,7 +5852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>294</v>
       </c>
@@ -5766,7 +5867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>295</v>
       </c>
@@ -5781,7 +5882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>296</v>
       </c>
@@ -5796,7 +5897,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>300</v>
       </c>
@@ -5810,7 +5911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>301</v>
       </c>
@@ -5824,7 +5925,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>302</v>
       </c>
@@ -5838,7 +5939,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>303</v>
       </c>
@@ -5852,7 +5953,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>304</v>
       </c>
@@ -5866,7 +5967,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>305</v>
       </c>
@@ -5880,7 +5981,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>306</v>
       </c>
@@ -5894,7 +5995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>307</v>
       </c>
@@ -5908,7 +6009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>308</v>
       </c>
@@ -5922,7 +6023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>309</v>
       </c>
@@ -5936,7 +6037,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>310</v>
       </c>
@@ -5950,7 +6051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>311</v>
       </c>
@@ -5964,7 +6065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>312</v>
       </c>
@@ -5978,7 +6079,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>313</v>
       </c>
@@ -5992,7 +6093,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>297</v>
       </c>
@@ -6006,7 +6107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>314</v>
       </c>
@@ -6020,7 +6121,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>315</v>
       </c>
@@ -6034,7 +6135,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>316</v>
       </c>
@@ -6048,7 +6149,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>317</v>
       </c>
@@ -6062,7 +6163,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>318</v>
       </c>
@@ -6076,7 +6177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>319</v>
       </c>
@@ -6090,7 +6191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>298</v>
       </c>
@@ -6104,7 +6205,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>320</v>
       </c>
@@ -6118,7 +6219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>321</v>
       </c>
@@ -6132,7 +6233,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>322</v>
       </c>
@@ -6146,7 +6247,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>323</v>
       </c>
@@ -6160,7 +6261,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>324</v>
       </c>
@@ -6174,7 +6275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>325</v>
       </c>
@@ -6188,7 +6289,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>326</v>
       </c>
@@ -6202,7 +6303,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>327</v>
       </c>
@@ -6216,7 +6317,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>328</v>
       </c>
@@ -6230,7 +6331,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>299</v>
       </c>
@@ -6244,7 +6345,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>329</v>
       </c>
@@ -6258,7 +6359,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>330</v>
       </c>
@@ -6272,7 +6373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>331</v>
       </c>
@@ -6286,7 +6387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>332</v>
       </c>
@@ -6300,7 +6401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>333</v>
       </c>
@@ -6314,7 +6415,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>334</v>
       </c>
@@ -6326,6 +6427,496 @@
       </c>
       <c r="D332">
         <v>6</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>335</v>
+      </c>
+      <c r="B333">
+        <v>1471</v>
+      </c>
+      <c r="C333">
+        <v>1471</v>
+      </c>
+      <c r="D333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>336</v>
+      </c>
+      <c r="B334">
+        <v>1472</v>
+      </c>
+      <c r="C334">
+        <v>1479</v>
+      </c>
+      <c r="D334">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>337</v>
+      </c>
+      <c r="B335">
+        <v>1480</v>
+      </c>
+      <c r="C335">
+        <v>1521</v>
+      </c>
+      <c r="D335">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>338</v>
+      </c>
+      <c r="B336">
+        <v>1522</v>
+      </c>
+      <c r="C336">
+        <v>1523</v>
+      </c>
+      <c r="D336">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>339</v>
+      </c>
+      <c r="B337">
+        <v>1524</v>
+      </c>
+      <c r="C337">
+        <v>1568</v>
+      </c>
+      <c r="D337">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>340</v>
+      </c>
+      <c r="B338">
+        <v>1569</v>
+      </c>
+      <c r="C338">
+        <v>1620</v>
+      </c>
+      <c r="D338">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>341</v>
+      </c>
+      <c r="B339">
+        <v>1621</v>
+      </c>
+      <c r="C339">
+        <v>1691</v>
+      </c>
+      <c r="D339">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>342</v>
+      </c>
+      <c r="B340">
+        <v>1692</v>
+      </c>
+      <c r="C340">
+        <v>1739</v>
+      </c>
+      <c r="D340">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>343</v>
+      </c>
+      <c r="B341">
+        <v>1740</v>
+      </c>
+      <c r="C341">
+        <v>1773</v>
+      </c>
+      <c r="D341">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>344</v>
+      </c>
+      <c r="B342">
+        <v>1774</v>
+      </c>
+      <c r="C342">
+        <v>1778</v>
+      </c>
+      <c r="D342">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>345</v>
+      </c>
+      <c r="B343">
+        <v>1779</v>
+      </c>
+      <c r="C343">
+        <v>1842</v>
+      </c>
+      <c r="D343">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>346</v>
+      </c>
+      <c r="B344">
+        <v>1843</v>
+      </c>
+      <c r="C344">
+        <v>1884</v>
+      </c>
+      <c r="D344">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>347</v>
+      </c>
+      <c r="B345">
+        <v>1885</v>
+      </c>
+      <c r="C345">
+        <v>1906</v>
+      </c>
+      <c r="D345">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>348</v>
+      </c>
+      <c r="B346">
+        <v>1907</v>
+      </c>
+      <c r="C346">
+        <v>2028</v>
+      </c>
+      <c r="D346">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>349</v>
+      </c>
+      <c r="B347">
+        <v>2029</v>
+      </c>
+      <c r="C347">
+        <v>2055</v>
+      </c>
+      <c r="D347">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>350</v>
+      </c>
+      <c r="B348">
+        <v>2056</v>
+      </c>
+      <c r="C348">
+        <v>2109</v>
+      </c>
+      <c r="D348">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>351</v>
+      </c>
+      <c r="B349">
+        <v>2110</v>
+      </c>
+      <c r="C349">
+        <v>2174</v>
+      </c>
+      <c r="D349">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>352</v>
+      </c>
+      <c r="B350">
+        <v>2175</v>
+      </c>
+      <c r="C350">
+        <v>2220</v>
+      </c>
+      <c r="D350">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>353</v>
+      </c>
+      <c r="B351">
+        <v>2221</v>
+      </c>
+      <c r="C351">
+        <v>2324</v>
+      </c>
+      <c r="D351">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>354</v>
+      </c>
+      <c r="B352">
+        <v>2325</v>
+      </c>
+      <c r="C352">
+        <v>2333</v>
+      </c>
+      <c r="D352">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>355</v>
+      </c>
+      <c r="B353">
+        <v>2334</v>
+      </c>
+      <c r="C353">
+        <v>2355</v>
+      </c>
+      <c r="D353">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>356</v>
+      </c>
+      <c r="B354">
+        <v>2356</v>
+      </c>
+      <c r="C354">
+        <v>2357</v>
+      </c>
+      <c r="D354">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>357</v>
+      </c>
+      <c r="B355">
+        <v>2358</v>
+      </c>
+      <c r="C355">
+        <v>2389</v>
+      </c>
+      <c r="D355">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>358</v>
+      </c>
+      <c r="B356">
+        <v>2390</v>
+      </c>
+      <c r="C356">
+        <v>2455</v>
+      </c>
+      <c r="D356">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>359</v>
+      </c>
+      <c r="B357">
+        <v>2456</v>
+      </c>
+      <c r="C357">
+        <v>2508</v>
+      </c>
+      <c r="D357">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>360</v>
+      </c>
+      <c r="B358">
+        <v>2509</v>
+      </c>
+      <c r="C358">
+        <v>2540</v>
+      </c>
+      <c r="D358">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>361</v>
+      </c>
+      <c r="B359">
+        <v>2541</v>
+      </c>
+      <c r="C359">
+        <v>2588</v>
+      </c>
+      <c r="D359">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>362</v>
+      </c>
+      <c r="B360">
+        <v>2589</v>
+      </c>
+      <c r="C360">
+        <v>2619</v>
+      </c>
+      <c r="D360">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>363</v>
+      </c>
+      <c r="B361">
+        <v>2620</v>
+      </c>
+      <c r="C361">
+        <v>2633</v>
+      </c>
+      <c r="D361">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>364</v>
+      </c>
+      <c r="B362">
+        <v>2634</v>
+      </c>
+      <c r="C362">
+        <v>2638</v>
+      </c>
+      <c r="D362">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>365</v>
+      </c>
+      <c r="B363">
+        <v>2639</v>
+      </c>
+      <c r="C363">
+        <v>2765</v>
+      </c>
+      <c r="D363">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>366</v>
+      </c>
+      <c r="B364">
+        <v>2766</v>
+      </c>
+      <c r="C364">
+        <v>2783</v>
+      </c>
+      <c r="D364">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>367</v>
+      </c>
+      <c r="B365">
+        <v>2784</v>
+      </c>
+      <c r="C365">
+        <v>2827</v>
+      </c>
+      <c r="D365">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>368</v>
+      </c>
+      <c r="B366">
+        <v>2828</v>
+      </c>
+      <c r="C366">
+        <v>2875</v>
+      </c>
+      <c r="D366">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>369</v>
+      </c>
+      <c r="B367">
+        <v>2876</v>
+      </c>
+      <c r="C367">
+        <v>2930</v>
+      </c>
+      <c r="D367">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
